--- a/data/trans_orig/P1432-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1432-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de incontinencia urinaria en 2007</t>
+          <t>Población con diagnóstico de incontinencia urinaria en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>1007</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11947</t>
+          <t>11829</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4724</t>
+          <t>4747</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1690</t>
+          <t>1822</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11878</t>
+          <t>12960</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>461829</t>
+          <t>461947</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>472762</t>
+          <t>472769</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>301956</t>
+          <t>301933</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>768579</t>
+          <t>767497</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>778767</t>
+          <t>778635</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,77%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1726</t>
+          <t>1732</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10096</t>
+          <t>10264</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10972</t>
+          <t>10756</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3973</t>
+          <t>3746</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15943</t>
+          <t>15832</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>356838</t>
+          <t>356670</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>365208</t>
+          <t>365202</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>360893</t>
+          <t>361109</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>370841</t>
+          <t>370846</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>722856</t>
+          <t>722967</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>734826</t>
+          <t>735053</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,49%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2592</t>
+          <t>2068</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13791</t>
+          <t>13492</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>7863</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3113</t>
+          <t>3930</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15796</t>
+          <t>16843</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>528598</t>
+          <t>528897</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>539797</t>
+          <t>540321</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>159696</t>
+          <t>159919</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>694375</t>
+          <t>693328</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>707058</t>
+          <t>706241</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,45%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9605</t>
+          <t>10065</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25329</t>
+          <t>25536</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2163</t>
+          <t>2165</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12104</t>
+          <t>11947</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13855</t>
+          <t>13414</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32373</t>
+          <t>31505</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1213005</t>
+          <t>1212798</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1228729</t>
+          <t>1228269</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>702181</t>
+          <t>702338</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>712122</t>
+          <t>712120</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1920247</t>
+          <t>1921115</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1938765</t>
+          <t>1939206</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,31%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1853</t>
+          <t>1668</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10955</t>
+          <t>9660</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5834</t>
+          <t>5562</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21003</t>
+          <t>19846</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9024</t>
+          <t>9208</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>24932</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>339600</t>
+          <t>340895</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>348702</t>
+          <t>348887</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>547749</t>
+          <t>548906</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>562918</t>
+          <t>563190</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>893117</t>
+          <t>894375</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>910283</t>
+          <t>910099</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,0%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1864</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17474</t>
+          <t>16689</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>38714</t>
+          <t>38258</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17201</t>
+          <t>17483</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>37912</t>
+          <t>39837</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>296337</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>298201</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1210046</t>
+          <t>1210502</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1231286</t>
+          <t>1232071</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1509048</t>
+          <t>1507123</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1529759</t>
+          <t>1529477</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25407</t>
+          <t>25256</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>49498</t>
+          <t>49162</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>38012</t>
+          <t>36860</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>67809</t>
+          <t>65059</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>68700</t>
+          <t>67844</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>106612</t>
+          <t>107173</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3220692</t>
+          <t>3221028</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3244783</t>
+          <t>3244934</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3310315</t>
+          <t>3313065</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3340112</t>
+          <t>3341264</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6541702</t>
+          <t>6541141</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6579614</t>
+          <t>6580470</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,98%</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3172,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de incontinencia urinaria en 2012</t>
+          <t>Población con diagnóstico de incontinencia urinaria en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4726</t>
+          <t>4801</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>980</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8475</t>
+          <t>10417</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>1089</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10194</t>
+          <t>10382</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>432485</t>
+          <t>432410</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>305979</t>
+          <t>304037</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>313478</t>
+          <t>313474</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3530,7 +3530,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>741471</t>
+          <t>741283</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>750614</t>
+          <t>750576</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5917</t>
+          <t>5229</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3745,62 +3745,62 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1030</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2120</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>5183</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1030</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>5191</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -3823,7 +3823,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>412880</t>
+          <t>413568</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>335891</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>338011</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>751617</t>
+          <t>751625</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3072</t>
+          <t>3107</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17648</t>
+          <t>18209</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>940</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8249</t>
+          <t>8077</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>4944</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19765</t>
+          <t>19269</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>611767</t>
+          <t>611206</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>626343</t>
+          <t>626308</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>251880</t>
+          <t>252052</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>259193</t>
+          <t>259189</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>869779</t>
+          <t>870275</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>884376</t>
+          <t>884600</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,44%</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5077</t>
+          <t>5041</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20390</t>
+          <t>18657</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4411,82 +4411,82 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>5126</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1960</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>11975</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>15216</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>8480</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>25658</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>0,44%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>5126</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1985</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>11482</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>15216</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>8165</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>24168</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1138619</t>
+          <t>1140352</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1153932</t>
+          <t>1153968</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4524,82 +4524,82 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>99,57%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>759596</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>752747</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>762762</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>99,33%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>98,43%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>99,74%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1779</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1908515</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>1898073</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>1915251</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>99,21%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>98,67%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>99,56%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>705</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>759596</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>753240</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>762737</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,33%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>98,5%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,74%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1779</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1908515</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1899563</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1915566</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>99,21%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>98,74%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>99,58%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9027</t>
+          <t>7841</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4759,7 +4759,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12995</t>
+          <t>13597</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30632</t>
+          <t>32795</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15755</t>
+          <t>16964</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37373</t>
+          <t>37230</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>501569</t>
+          <t>502755</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>509582</t>
+          <t>509587</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>729614</t>
+          <t>727451</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>747251</t>
+          <t>746649</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1233470</t>
+          <t>1233613</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1255088</t>
+          <t>1253879</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,67%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15936</t>
+          <t>16142</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37239</t>
+          <t>37518</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16131</t>
+          <t>16224</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>39704</t>
+          <t>37699</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -5195,12 +5195,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>264956</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>266882</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1071004</t>
+          <t>1070725</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1092307</t>
+          <t>1092101</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1335421</t>
+          <t>1337426</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1358994</t>
+          <t>1358901</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,82%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14057</t>
+          <t>13985</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>35360</t>
+          <t>33761</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>44309</t>
+          <t>43163</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>75766</t>
+          <t>75162</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>62836</t>
+          <t>63593</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>101384</t>
+          <t>102076</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3386550</t>
+          <t>3388149</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3407853</t>
+          <t>3407925</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3470040</t>
+          <t>3470644</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3501497</t>
+          <t>3502643</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6866332</t>
+          <t>6865640</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6904880</t>
+          <t>6904123</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>
@@ -5807,7 +5807,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de incontinencia urinaria en 2016</t>
+          <t>Población con diagnóstico de incontinencia urinaria en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6481</t>
+          <t>5942</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6022,7 +6022,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6042,7 +6042,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8555</t>
+          <t>8556</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6057,7 +6057,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6072,12 +6072,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1256</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10639</t>
+          <t>11078</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -6115,7 +6115,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>422611</t>
+          <t>423150</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>338500</t>
+          <t>338499</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>765508</t>
+          <t>765069</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>774947</t>
+          <t>774891</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,84%</t>
         </is>
       </c>
     </row>
@@ -6350,7 +6350,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5801</t>
+          <t>5917</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1057</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15013</t>
+          <t>14839</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6415,12 +6415,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2135</t>
+          <t>2247</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15283</t>
+          <t>15316</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -6458,7 +6458,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>371426</t>
+          <t>371310</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -6473,7 +6473,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6493,12 +6493,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>357260</t>
+          <t>357434</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>371216</t>
+          <t>371223</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>734217</t>
+          <t>734184</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>747365</t>
+          <t>747253</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,7%</t>
         </is>
       </c>
     </row>
@@ -6688,12 +6688,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>782</t>
+          <t>777</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9726</t>
+          <t>9844</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6728,7 +6728,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7958</t>
+          <t>8185</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6743,7 +6743,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6758,12 +6758,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1873</t>
+          <t>2179</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12309</t>
+          <t>13288</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6773,12 +6773,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -6801,12 +6801,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>512188</t>
+          <t>512070</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>521132</t>
+          <t>521137</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>158165</t>
+          <t>157938</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -6851,7 +6851,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -6871,12 +6871,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>675727</t>
+          <t>674748</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>686163</t>
+          <t>685857</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,68%</t>
         </is>
       </c>
     </row>
@@ -7031,12 +7031,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1636</t>
+          <t>1645</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10229</t>
+          <t>9762</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4397</t>
+          <t>3880</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18271</t>
+          <t>17616</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7815</t>
+          <t>7442</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23239</t>
+          <t>22778</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -7144,12 +7144,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1139409</t>
+          <t>1139876</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1148002</t>
+          <t>1147993</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7159,7 +7159,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7179,12 +7179,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>807605</t>
+          <t>808260</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>821479</t>
+          <t>821996</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1952275</t>
+          <t>1952736</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1967699</t>
+          <t>1968072</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,62%</t>
         </is>
       </c>
     </row>
@@ -7374,12 +7374,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2576</t>
+          <t>2569</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11413</t>
+          <t>12175</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3317</t>
+          <t>3221</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15883</t>
+          <t>15601</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7593</t>
+          <t>7942</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22789</t>
+          <t>23748</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -7487,12 +7487,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>609293</t>
+          <t>608531</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>618130</t>
+          <t>618137</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>722361</t>
+          <t>722643</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>734927</t>
+          <t>735023</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1336161</t>
+          <t>1335202</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1351357</t>
+          <t>1351008</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,42%</t>
         </is>
       </c>
     </row>
@@ -7717,12 +7717,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16019</t>
+          <t>15717</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36966</t>
+          <t>37404</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17028</t>
+          <t>16422</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>39034</t>
+          <t>37450</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -7830,12 +7830,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>285126</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>287145</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1045059</t>
+          <t>1044621</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1066006</t>
+          <t>1066308</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1330136</t>
+          <t>1331720</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1352142</t>
+          <t>1352748</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -8060,12 +8060,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10457</t>
+          <t>10209</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28030</t>
+          <t>27170</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>38012</t>
+          <t>36903</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>67577</t>
+          <t>67667</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>52605</t>
+          <t>52118</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>87812</t>
+          <t>88862</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -8173,12 +8173,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3357692</t>
+          <t>3358552</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3375265</t>
+          <t>3375513</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3464019</t>
+          <t>3463929</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3493584</t>
+          <t>3494693</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6829506</t>
+          <t>6828456</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6864713</t>
+          <t>6865200</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,25%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1432-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1432-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1007</t>
+          <t>983</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11829</t>
+          <t>10876</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4747</t>
+          <t>4342</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1822</t>
+          <t>1814</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12960</t>
+          <t>12293</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>461947</t>
+          <t>462900</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>472769</t>
+          <t>472793</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>301933</t>
+          <t>302338</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>767497</t>
+          <t>768164</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>778635</t>
+          <t>778643</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1732</t>
+          <t>1751</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10264</t>
+          <t>10189</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10756</t>
+          <t>11083</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3746</t>
+          <t>3926</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15832</t>
+          <t>15699</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>356670</t>
+          <t>356745</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>365202</t>
+          <t>365183</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>361109</t>
+          <t>360782</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>370846</t>
+          <t>370830</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>722967</t>
+          <t>723100</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>735053</t>
+          <t>734873</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2068</t>
+          <t>1888</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13492</t>
+          <t>12524</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7863</t>
+          <t>8073</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3930</t>
+          <t>3827</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16843</t>
+          <t>16619</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>528897</t>
+          <t>529865</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>540321</t>
+          <t>540501</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>159919</t>
+          <t>159709</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>693328</t>
+          <t>693552</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>706241</t>
+          <t>706344</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10065</t>
+          <t>9510</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25536</t>
+          <t>25385</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2165</t>
+          <t>2033</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11947</t>
+          <t>11685</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13414</t>
+          <t>14688</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31505</t>
+          <t>32855</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1212798</t>
+          <t>1212949</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1228269</t>
+          <t>1228824</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>702338</t>
+          <t>702600</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>712120</t>
+          <t>712252</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1921115</t>
+          <t>1919765</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1939206</t>
+          <t>1937932</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,25%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1668</t>
+          <t>1834</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9660</t>
+          <t>9806</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5562</t>
+          <t>5392</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19846</t>
+          <t>20001</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9208</t>
+          <t>8832</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24932</t>
+          <t>25598</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>340895</t>
+          <t>340749</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>348887</t>
+          <t>348721</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>548906</t>
+          <t>548751</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>563190</t>
+          <t>563360</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>894375</t>
+          <t>893709</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>910099</t>
+          <t>910475</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16689</t>
+          <t>16917</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>38258</t>
+          <t>38133</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17483</t>
+          <t>17093</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>39837</t>
+          <t>37991</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1210502</t>
+          <t>1210627</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1232071</t>
+          <t>1231843</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1507123</t>
+          <t>1508969</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1529477</t>
+          <t>1529867</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25256</t>
+          <t>25839</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>49162</t>
+          <t>49629</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,39 +2805,39 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>50689</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>36718</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>65441</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
           <t>1,5%</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>50689</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>36860</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>65059</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
           <t>1,09%</t>
@@ -2845,7 +2845,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>67844</t>
+          <t>69098</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>107173</t>
+          <t>108864</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3221028</t>
+          <t>3220561</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3244934</t>
+          <t>3244351</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,42 +2918,42 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
+          <t>98,48%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>99,21%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>3248</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>3327435</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>3312683</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>3341406</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
           <t>98,5%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>99,23%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>3248</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>3327435</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>3313065</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>3341264</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>98,5%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6541141</t>
+          <t>6539450</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6580470</t>
+          <t>6579216</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4801</t>
+          <t>4742</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>957</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10417</t>
+          <t>8211</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>1038</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10382</t>
+          <t>10374</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>432410</t>
+          <t>432469</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>304037</t>
+          <t>306243</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>313474</t>
+          <t>313497</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>741283</t>
+          <t>741291</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>750576</t>
+          <t>750627</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5229</t>
+          <t>6170</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>5170</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>413568</t>
+          <t>412627</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>751625</t>
+          <t>751638</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3107</t>
+          <t>3077</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18209</t>
+          <t>16981</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4093,7 +4093,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8077</t>
+          <t>8157</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4944</t>
+          <t>5149</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19269</t>
+          <t>20010</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>611206</t>
+          <t>612434</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>626308</t>
+          <t>626338</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>252052</t>
+          <t>251972</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>870275</t>
+          <t>869534</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>884600</t>
+          <t>884395</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,42%</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5041</t>
+          <t>4135</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18657</t>
+          <t>19398</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4411,82 +4411,82 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>5126</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1944</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>11192</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>15216</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>8243</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>25412</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>0,43%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>5126</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1960</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>11975</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>15216</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>8480</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>25658</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1140352</t>
+          <t>1139611</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1153968</t>
+          <t>1154874</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4524,82 +4524,82 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>99,64%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>759596</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>753530</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>762778</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>99,33%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>98,54%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>99,75%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1779</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1908515</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>1898319</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>1915488</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>99,21%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>98,68%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>99,57%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>705</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>759596</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>752747</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>762762</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,33%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>98,43%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,74%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1779</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1908515</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1898073</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1915251</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>99,21%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>98,67%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>99,56%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7841</t>
+          <t>8363</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4759,7 +4759,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13597</t>
+          <t>12886</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32795</t>
+          <t>31126</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16964</t>
+          <t>15601</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37230</t>
+          <t>36059</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>502755</t>
+          <t>502233</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>509587</t>
+          <t>509586</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>727451</t>
+          <t>729120</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>746649</t>
+          <t>747360</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1233613</t>
+          <t>1234784</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1253879</t>
+          <t>1255242</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,77%</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16142</t>
+          <t>16085</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37518</t>
+          <t>37462</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16224</t>
+          <t>16529</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>37699</t>
+          <t>38310</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1070725</t>
+          <t>1070781</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1092101</t>
+          <t>1092158</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1337426</t>
+          <t>1336815</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1358901</t>
+          <t>1358596</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13985</t>
+          <t>13302</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>33761</t>
+          <t>36156</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>43163</t>
+          <t>43906</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>75162</t>
+          <t>75805</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>63593</t>
+          <t>64399</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>102076</t>
+          <t>101261</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3388149</t>
+          <t>3385754</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3407925</t>
+          <t>3408608</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3470644</t>
+          <t>3470001</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3502643</t>
+          <t>3501900</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6865640</t>
+          <t>6866455</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6904123</t>
+          <t>6903317</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5942</t>
+          <t>5604</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6022,7 +6022,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6042,7 +6042,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8556</t>
+          <t>7549</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6057,7 +6057,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6072,12 +6072,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1256</t>
+          <t>992</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11078</t>
+          <t>10994</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -6115,7 +6115,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>423150</t>
+          <t>423488</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>338499</t>
+          <t>339506</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>765069</t>
+          <t>765153</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>774891</t>
+          <t>775155</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,87%</t>
         </is>
       </c>
     </row>
@@ -6350,7 +6350,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5917</t>
+          <t>6291</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14839</t>
+          <t>13703</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6415,12 +6415,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2247</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15316</t>
+          <t>16019</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -6458,7 +6458,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>371310</t>
+          <t>370936</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -6473,7 +6473,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6493,12 +6493,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>357434</t>
+          <t>358570</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>371223</t>
+          <t>371220</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>734184</t>
+          <t>733481</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>747253</t>
+          <t>747290</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,71%</t>
         </is>
       </c>
     </row>
@@ -6688,12 +6688,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>777</t>
+          <t>782</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9844</t>
+          <t>10199</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6728,7 +6728,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8185</t>
+          <t>7197</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6743,7 +6743,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6758,12 +6758,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>2251</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13288</t>
+          <t>12744</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6773,12 +6773,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -6801,12 +6801,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>512070</t>
+          <t>511715</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>521137</t>
+          <t>521132</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>157938</t>
+          <t>158926</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -6851,7 +6851,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -6871,12 +6871,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>674748</t>
+          <t>675292</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>685857</t>
+          <t>685785</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,67%</t>
         </is>
       </c>
     </row>
@@ -7031,12 +7031,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1645</t>
+          <t>1739</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9762</t>
+          <t>9665</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3880</t>
+          <t>4138</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17616</t>
+          <t>16723</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7442</t>
+          <t>7608</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22778</t>
+          <t>23101</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -7144,12 +7144,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1139876</t>
+          <t>1139973</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1147993</t>
+          <t>1147899</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7179,12 +7179,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>808260</t>
+          <t>809153</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>821996</t>
+          <t>821738</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1952736</t>
+          <t>1952413</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1968072</t>
+          <t>1967906</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,61%</t>
         </is>
       </c>
     </row>
@@ -7374,12 +7374,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2569</t>
+          <t>2482</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12175</t>
+          <t>11112</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3221</t>
+          <t>3372</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15601</t>
+          <t>15474</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7942</t>
+          <t>8058</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23748</t>
+          <t>22048</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -7487,12 +7487,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>608531</t>
+          <t>609594</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>618137</t>
+          <t>618224</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>722643</t>
+          <t>722770</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>735023</t>
+          <t>734872</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1335202</t>
+          <t>1336902</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1351008</t>
+          <t>1350892</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -7697,7 +7697,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15717</t>
+          <t>15967</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37404</t>
+          <t>36671</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16422</t>
+          <t>15331</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>37450</t>
+          <t>36873</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -7865,12 +7865,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1044621</t>
+          <t>1045354</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1066308</t>
+          <t>1066058</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1331720</t>
+          <t>1332297</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1352748</t>
+          <t>1353839</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,88%</t>
         </is>
       </c>
     </row>
@@ -8060,12 +8060,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10209</t>
+          <t>10711</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27170</t>
+          <t>27533</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>36903</t>
+          <t>37076</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>67667</t>
+          <t>67696</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8110,7 +8110,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>52118</t>
+          <t>52589</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>88862</t>
+          <t>87031</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -8173,12 +8173,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3358552</t>
+          <t>3358189</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3375513</t>
+          <t>3375011</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3463929</t>
+          <t>3463900</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3494693</t>
+          <t>3494520</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6828456</t>
+          <t>6830287</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6865200</t>
+          <t>6864729</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,24%</t>
         </is>
       </c>
     </row>
